--- a/reports/2026-10-04.xlsx
+++ b/reports/2026-10-04.xlsx
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2728.659999999998</v>
+        <v>2733.369999999999</v>
       </c>
     </row>
     <row r="12">
